--- a/reports/seo_intel_2026-W25.xlsx
+++ b/reports/seo_intel_2026-W25.xlsx
@@ -462,7 +462,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-15 10:57 UTC</t>
+          <t>Generated: 2026-06-15 18:07 UTC</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-15 10:57 UTC</t>
+          <t>Generated: 2026-06-15 18:07 UTC</t>
         </is>
       </c>
     </row>
